--- a/data/trans_dic/P57B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57B_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat)</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,14</t>
+          <t>2,06; 7,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,21</t>
+          <t>4,43; 8,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,89</t>
+          <t>3,59; 6,89</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,01</t>
+          <t>2,15; 6,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,69</t>
+          <t>5,12; 8,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 6,89</t>
+          <t>4,07; 6,87</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,09; 14,28</t>
+          <t>8,18; 14,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,61; 18,41</t>
+          <t>12,52; 18,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,16; 15,46</t>
+          <t>11,21; 15,37</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,92</t>
+          <t>4,93; 12,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 13,51</t>
+          <t>5,63; 13,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,05; 11,55</t>
+          <t>6,17; 11,33</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,77; 29,31</t>
+          <t>18,47; 29,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,73; 36,18</t>
+          <t>27,63; 36,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,94; 31,36</t>
+          <t>24,64; 31,42</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 17,89</t>
+          <t>11,2; 17,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,33; 23,18</t>
+          <t>16,19; 23,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,47; 19,39</t>
+          <t>14,24; 19,25</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 10,0</t>
+          <t>5,36; 10,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 11,03</t>
+          <t>3,79; 11,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,55; 9,53</t>
+          <t>4,5; 9,66</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 17,3</t>
+          <t>5,26; 17,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,43; 24,62</t>
+          <t>19,61; 24,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,96; 19,88</t>
+          <t>9,03; 19,83</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,44; 10,69</t>
+          <t>7,46; 10,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,05; 14,98</t>
+          <t>11,04; 14,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,85; 12,48</t>
+          <t>10,04; 12,56</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat)</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6734; 22130</t>
+          <t>6392; 23643</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12913; 23786</t>
+          <t>12817; 24672</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21274; 41352</t>
+          <t>21520; 41338</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11126; 30665</t>
+          <t>10958; 32628</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25660; 44064</t>
+          <t>25947; 44702</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40930; 70091</t>
+          <t>41345; 69864</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24984; 44121</t>
+          <t>25272; 45466</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42065; 61399</t>
+          <t>41768; 60883</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71734; 99308</t>
+          <t>72034; 98740</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13011; 35000</t>
+          <t>14474; 37147</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24169; 60481</t>
+          <t>25210; 60006</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44844; 85615</t>
+          <t>45749; 84012</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33235; 51891</t>
+          <t>32704; 51974</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>57431; 74942</t>
+          <t>57225; 74864</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95810; 120478</t>
+          <t>94666; 120689</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29814; 48092</t>
+          <t>30105; 47999</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41978; 59574</t>
+          <t>41617; 59682</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76122; 101963</t>
+          <t>74897; 101222</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>33237; 62097</t>
+          <t>33299; 62575</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32441; 93077</t>
+          <t>31961; 96236</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66666; 139609</t>
+          <t>65886; 141549</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>48473; 160329</t>
+          <t>48730; 161663</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>139269; 176432</t>
+          <t>140549; 175731</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>163590; 326743</t>
+          <t>148455; 325791</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>254253; 365385</t>
+          <t>254826; 366914</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>397967; 539590</t>
+          <t>397866; 534397</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>691136; 875819</t>
+          <t>704388; 881414</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57B_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,62</t>
+          <t>1,89; 6,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 8,52</t>
+          <t>4,7; 8,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,89</t>
+          <t>3,73; 6,59</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,4</t>
+          <t>2,23; 6,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,82</t>
+          <t>4,96; 8,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,87</t>
+          <t>3,97; 6,53</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 14,71</t>
+          <t>8,23; 14,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,52; 18,25</t>
+          <t>12,71; 18,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,21; 15,37</t>
+          <t>11,26; 15,5</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 12,65</t>
+          <t>3,99; 10,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 13,4</t>
+          <t>9,49; 15,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 11,33</t>
+          <t>7,61; 12,16</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,47; 29,36</t>
+          <t>18,76; 28,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,63; 36,15</t>
+          <t>27,37; 35,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,64; 31,42</t>
+          <t>24,67; 31,04</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,2; 17,85</t>
+          <t>11,7; 18,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,19; 23,22</t>
+          <t>16,55; 23,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,24; 19,25</t>
+          <t>14,87; 19,83</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,08</t>
+          <t>5,28; 9,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 11,41</t>
+          <t>8,32; 12,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 9,66</t>
+          <t>7,42; 10,52</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,26; 17,45</t>
+          <t>13,66; 18,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,61; 24,52</t>
+          <t>19,53; 24,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,03; 19,83</t>
+          <t>17,33; 20,95</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,46; 10,74</t>
+          <t>9,24; 11,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,04; 14,83</t>
+          <t>13,77; 15,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,04; 12,56</t>
+          <t>11,89; 13,27</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30258</t>
+          <t>31496</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6392; 23643</t>
+          <t>5999; 19714</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12817; 24672</t>
+          <t>14847; 26907</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21520; 41338</t>
+          <t>23641; 41755</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>19054</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>34249</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53303</t>
+          <t>54559</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10958; 32628</t>
+          <t>11660; 32168</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25947; 44702</t>
+          <t>26705; 45718</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41345; 69864</t>
+          <t>42115; 69295</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33482</t>
+          <t>34561</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50964</t>
+          <t>53308</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84446</t>
+          <t>87869</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25272; 45466</t>
+          <t>25446; 44569</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41768; 60883</t>
+          <t>43549; 63956</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72034; 98740</t>
+          <t>73384; 101021</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22001</t>
+          <t>23447</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>44205</t>
+          <t>47838</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66206</t>
+          <t>71286</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14474; 37147</t>
+          <t>13858; 36374</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25210; 60006</t>
+          <t>37049; 60723</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45749; 84012</t>
+          <t>56204; 89731</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41872</t>
+          <t>48177</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>65984</t>
+          <t>70688</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107856</t>
+          <t>118864</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32704; 51974</t>
+          <t>38257; 58682</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>57225; 74864</t>
+          <t>61749; 80479</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94666; 120689</t>
+          <t>105956; 133350</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>37932</t>
+          <t>40205</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>50331</t>
+          <t>52546</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88263</t>
+          <t>92751</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>30105; 47999</t>
+          <t>31598; 50305</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41617; 59682</t>
+          <t>43656; 62279</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74897; 101222</t>
+          <t>79361; 105836</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>44724</t>
+          <t>51139</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>66634</t>
+          <t>79413</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>111358</t>
+          <t>130552</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>33299; 62575</t>
+          <t>37778; 69073</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31961; 96236</t>
+          <t>63537; 96730</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65886; 141549</t>
+          <t>109860; 155646</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>112189</t>
+          <t>127472</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>157232</t>
+          <t>182594</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>269421</t>
+          <t>310066</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>48730; 161663</t>
+          <t>108689; 149843</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>140549; 175731</t>
+          <t>162124; 202635</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>148455; 325791</t>
+          <t>281836; 340605</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>323628</t>
+          <t>355911</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>487482</t>
+          <t>541532</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>811110</t>
+          <t>897443</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>254826; 366914</t>
+          <t>321937; 393887</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>397866; 534397</t>
+          <t>505520; 575781</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>704388; 881414</t>
+          <t>850906; 949298</t>
         </is>
       </c>
     </row>
